--- a/excel_upload_masters/templates/12_billing_taggd_workflow.xlsx
+++ b/excel_upload_masters/templates/12_billing_taggd_workflow.xlsx
@@ -4,15 +4,16 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="taggd_revenue_billing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="finance_billing_workflow" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="finance_billing_validation_even" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="finance_payment_receipts" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="finance_tds_certificates" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="finance_bank_statement_lines" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lists" sheetId="1" state="hidden" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="taggd_revenue_billing" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="finance_billing_workflow" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="finance_billing_validation_even" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="finance_payment_receipts" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="finance_tds_certificates" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="finance_bank_statement_lines" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,6 +438,193 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>16A</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>submitted</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NEFT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>unmatched</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>16B</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>under_review</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>RTGS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>disputed</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>IMPS</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>unmatched</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>UPI</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>junior_approved</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>disputed</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cfo_pending</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>fully_approved</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:AJ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -720,7 +908,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -898,7 +1086,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Pick from list (dropdown)</t>
+        </is>
+      </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Date/datetime — ISO-8601 or Excel date</t>
@@ -917,12 +1109,24 @@
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Pick from list (dropdown)</t>
+        </is>
+      </c>
       <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Pick from list (dropdown)</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Pick from list (dropdown)</t>
+        </is>
+      </c>
       <c r="P2" s="2" t="inlineStr"/>
       <c r="Q2" s="2" t="inlineStr">
         <is>
@@ -935,8 +1139,16 @@
           <t>Date/datetime — ISO-8601 or Excel date</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr"/>
-      <c r="U2" s="2" t="inlineStr"/>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>Pick from list (dropdown)</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>Pick from list (dropdown)</t>
+        </is>
+      </c>
       <c r="V2" s="2" t="inlineStr"/>
       <c r="W2" s="2" t="inlineStr">
         <is>
@@ -961,11 +1173,31 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="6">
+    <dataValidation sqref="C3:C5002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the list, or clear the cell." type="list">
+      <formula1>=lists!$A$1:$A$8</formula1>
+    </dataValidation>
+    <dataValidation sqref="J3:J5002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the list, or clear the cell." type="list">
+      <formula1>=lists!$B$1:$B$9</formula1>
+    </dataValidation>
+    <dataValidation sqref="L3:L5002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the list, or clear the cell." type="list">
+      <formula1>=lists!$C$1:$C$2</formula1>
+    </dataValidation>
+    <dataValidation sqref="O3:O5002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the list, or clear the cell." type="list">
+      <formula1>=lists!$D$1:$D$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="T3:T5002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the list, or clear the cell." type="list">
+      <formula1>=lists!$C$1:$C$2</formula1>
+    </dataValidation>
+    <dataValidation sqref="U3:U5002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the list, or clear the cell." type="list">
+      <formula1>=lists!$E$1:$E$6</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1035,7 +1267,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1117,9 +1349,17 @@
           <t>Date/datetime — ISO-8601 or Excel date</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Pick from list (dropdown)</t>
+        </is>
+      </c>
       <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Pick from list (dropdown)</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
@@ -1129,11 +1369,19 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="E3:E5002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the list, or clear the cell." type="list">
+      <formula1>=lists!$B$1:$B$9</formula1>
+    </dataValidation>
+    <dataValidation sqref="G3:G5002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the list, or clear the cell." type="list">
+      <formula1>=lists!$C$1:$C$2</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1218,7 +1466,11 @@
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Pick from list (dropdown)</t>
+        </is>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Date/datetime — ISO-8601 or Excel date</t>
@@ -1234,11 +1486,16 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="F3:F5002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the list, or clear the cell." type="list">
+      <formula1>=lists!$F$1:$F$3</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
